--- a/extenbooks/S408_extenbook.xlsx
+++ b/extenbooks/S408_extenbook.xlsx
@@ -811,7 +811,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1880,11 +1880,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1907,76 +1907,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eiteman &amp; Guthrie 1952 cost-curve survey (cross_sectional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S408_research.json", "adequacy_report": "Technical/docs/chapters/CH4_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S408_DPR.md", "epr": "Technical/docs/series/S408_EPR.md", "loader": "Technical/code/L01_loaders/L01_S408_load.py", "processor": "Technical/code/P02_processors/P02_S408_construct.py", "validator": "Technical/code/V03_validators/V03_S408_validate.py", "processed": "Technical/data/processed/S408.parquet", "chopped_csv": "Technical/chopped/S408.csv", "extenbook_xlsx": "Technical/extenbooks/S408_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T21:57:52.480731+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
